--- a/school_surveys/018_remote_learning_survey_for_kindergarten_kids--school_surveys.xlsx
+++ b/school_surveys/018_remote_learning_survey_for_kindergarten_kids--school_surveys.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -665,8 +665,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="31" customWidth="1" min="1" max="1"/>
-    <col width="35" customWidth="1" min="2" max="2"/>
-    <col width="35" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -694,12 +694,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'value':_'daily'}</t>
+          <t>daily</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'value': 'daily'}</t>
+          <t>daily</t>
         </is>
       </c>
     </row>
@@ -711,12 +711,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'value':_'several_times_a_week'}</t>
+          <t>several_times_a_week</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'value': 'several times a week'}</t>
+          <t>several times a week</t>
         </is>
       </c>
     </row>
@@ -728,12 +728,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'value':_'rarely'}</t>
+          <t>rarely</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'value': 'rarely'}</t>
+          <t>rarely</t>
         </is>
       </c>
     </row>
@@ -745,12 +745,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'value':_'never'}</t>
+          <t>never</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'value': 'never'}</t>
+          <t>never</t>
         </is>
       </c>
     </row>
@@ -762,12 +762,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'value':_'email'}</t>
+          <t>email</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'value': 'email'}</t>
+          <t>email</t>
         </is>
       </c>
     </row>
@@ -779,12 +779,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'value':_'phone'}</t>
+          <t>phone</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'value': 'phone'}</t>
+          <t>phone</t>
         </is>
       </c>
     </row>
@@ -796,12 +796,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'value':_'messaging_app'}</t>
+          <t>messaging_app</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'value': 'messaging_app'}</t>
+          <t>messaging app</t>
         </is>
       </c>
     </row>
@@ -813,12 +813,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'value':_'video_call'}</t>
+          <t>video_call</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'value': 'video_call'}</t>
+          <t>video call</t>
         </is>
       </c>
     </row>
@@ -830,12 +830,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'value':_'technical_issues'}</t>
+          <t>technical_issues</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'value': 'technical_issues'}</t>
+          <t>technical issues</t>
         </is>
       </c>
     </row>
@@ -847,12 +847,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'value':_'time_management'}</t>
+          <t>time_management</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'value': 'time_management'}</t>
+          <t>time management</t>
         </is>
       </c>
     </row>
@@ -864,12 +864,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'value':_'lack_of_access'}</t>
+          <t>lack_of_access</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'value': 'lack_of_access'}</t>
+          <t>lack of access</t>
         </is>
       </c>
     </row>
@@ -881,12 +881,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'value':_'very_effective'}</t>
+          <t>very_effective</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'value': 'very_effective'}</t>
+          <t>very effective</t>
         </is>
       </c>
     </row>
@@ -898,12 +898,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'value':_'fairly_effective'}</t>
+          <t>fairly_effective</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'value': 'fairly_effective'}</t>
+          <t>fairly effective</t>
         </is>
       </c>
     </row>
@@ -915,12 +915,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'value':_'neutral'}</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'value': 'neutral'}</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -932,12 +932,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'value':_'not_effective'}</t>
+          <t>not_effective</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'value': 'not_effective'}</t>
+          <t>not effective</t>
         </is>
       </c>
     </row>
@@ -949,12 +949,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'value':_'very_not_effective'}</t>
+          <t>very_not_effective</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'value': 'very_not_effective'}</t>
+          <t>very not effective</t>
         </is>
       </c>
     </row>
